--- a/data/base_setra.xlsx
+++ b/data/base_setra.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AA64C5-BCBC-4A2D-9579-24C43FAC97E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -83,13 +89,22 @@
   </si>
   <si>
     <t>Custo</t>
+  </si>
+  <si>
+    <t>Locator_Bullla</t>
+  </si>
+  <si>
+    <t>::</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,24 +156,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +223,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,6 +257,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -264,9 +292,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -439,11 +468,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,6 +541,843 @@
       </c>
       <c r="W1" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>71</v>
+      </c>
+      <c r="D2">
+        <v>110</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>71</v>
+      </c>
+      <c r="D3">
+        <v>110</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>0.46150000000000002</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="S3" s="3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="3">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>71</v>
+      </c>
+      <c r="D4">
+        <v>110</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>11</v>
+      </c>
+      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>0.36359999999999998</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="S4" s="3">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4" s="3">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>0.33750000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>71</v>
+      </c>
+      <c r="D5">
+        <v>110</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" t="s">
+        <v>25</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>25</v>
+      </c>
+      <c r="V5" t="s">
+        <v>25</v>
+      </c>
+      <c r="W5">
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>71</v>
+      </c>
+      <c r="D6">
+        <v>110</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" t="s">
+        <v>25</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>25</v>
+      </c>
+      <c r="V6" t="s">
+        <v>25</v>
+      </c>
+      <c r="W6">
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B7">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>71</v>
+      </c>
+      <c r="D7">
+        <v>110</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" t="s">
+        <v>25</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" t="s">
+        <v>25</v>
+      </c>
+      <c r="W7">
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B8">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>71</v>
+      </c>
+      <c r="D8">
+        <v>110</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" t="s">
+        <v>25</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W8">
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B9">
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>71</v>
+      </c>
+      <c r="D9">
+        <v>110</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" t="s">
+        <v>25</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" t="s">
+        <v>25</v>
+      </c>
+      <c r="W9">
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>71</v>
+      </c>
+      <c r="D10">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10">
+        <v>10002</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="P10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" t="s">
+        <v>25</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10" t="s">
+        <v>25</v>
+      </c>
+      <c r="V10" s="5">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>71</v>
+      </c>
+      <c r="D11">
+        <v>110</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11">
+        <v>10002</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P11" s="4">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>71</v>
+      </c>
+      <c r="D12">
+        <v>110</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12">
+        <v>10002</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>1860</v>
+      </c>
+      <c r="J12">
+        <v>50</v>
+      </c>
+      <c r="K12">
+        <v>4</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>4</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="P12" s="4">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>2.69E-2</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>2.4580000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B13">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>71</v>
+      </c>
+      <c r="D13">
+        <v>110</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>10002</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>9212</v>
+      </c>
+      <c r="J13">
+        <v>228</v>
+      </c>
+      <c r="K13">
+        <v>13</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>13</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P13" s="4">
+        <v>1.2037037037037038E-3</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="R13" s="5">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5">
+        <v>0.93330000000000002</v>
+      </c>
+      <c r="W13">
+        <v>13.3232</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_setra.xlsx
+++ b/data/base_setra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AA64C5-BCBC-4A2D-9579-24C43FAC97E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166F8C5C-EAF8-4C50-A223-48F09FA81182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -469,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -1378,6 +1378,219 @@
       </c>
       <c r="W13">
         <v>13.3232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>71</v>
+      </c>
+      <c r="D14">
+        <v>110</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14">
+        <v>10002</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>11941</v>
+      </c>
+      <c r="J14">
+        <v>306</v>
+      </c>
+      <c r="K14">
+        <v>10</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>10</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="P14" s="4">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="R14" s="5">
+        <v>3.27E-2</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>33.895699999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>71</v>
+      </c>
+      <c r="D15">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15">
+        <v>10002</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>2316</v>
+      </c>
+      <c r="J15">
+        <v>27</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="P15" s="4">
+        <v>1.5625000000000001E-3</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>1.17E-2</v>
+      </c>
+      <c r="R15" s="5">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>2.7904</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B16">
+        <v>11</v>
+      </c>
+      <c r="C16">
+        <v>71</v>
+      </c>
+      <c r="D16">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16">
+        <v>10002</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>2995</v>
+      </c>
+      <c r="J16">
+        <v>54</v>
+      </c>
+      <c r="K16">
+        <v>3</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="P16" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="R16" s="5">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="S16" s="3">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16" t="s">
+        <v>25</v>
+      </c>
+      <c r="V16" t="s">
+        <v>25</v>
+      </c>
+      <c r="W16">
+        <v>10.864000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_setra.xlsx
+++ b/data/base_setra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166F8C5C-EAF8-4C50-A223-48F09FA81182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2179B4E-291D-484F-9F51-CB10D4756E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -469,8 +469,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1397,7 +1422,7 @@
         <v>23</v>
       </c>
       <c r="F14">
-        <v>10002</v>
+        <v>15474</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1468,7 +1493,7 @@
         <v>23</v>
       </c>
       <c r="F15">
-        <v>10002</v>
+        <v>15474</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -1539,58 +1564,555 @@
         <v>23</v>
       </c>
       <c r="F16">
-        <v>10002</v>
+        <v>15474</v>
       </c>
       <c r="G16">
         <v>10</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>2995</v>
+        <v>10375</v>
       </c>
       <c r="J16">
-        <v>54</v>
+        <v>219</v>
       </c>
       <c r="K16">
+        <v>12</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>11</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="P16" s="4">
+        <v>1.9097222222222222E-3</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="R16" s="5">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="S16" s="3">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16" s="5">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="V16" s="5">
+        <v>0.91669999999999996</v>
+      </c>
+      <c r="W16">
+        <v>29.5838</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>71</v>
+      </c>
+      <c r="D17">
+        <v>110</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17">
+        <v>15474</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17">
         <v>3</v>
       </c>
-      <c r="L16">
+      <c r="I17">
+        <v>20703</v>
+      </c>
+      <c r="J17">
+        <v>455</v>
+      </c>
+      <c r="K17">
+        <v>20</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>18</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" s="4">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="P17" s="4">
+        <v>1.3310185185185185E-3</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="R17" s="5">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>2</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="V17" s="5">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>51.725099999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>71</v>
+      </c>
+      <c r="D18">
+        <v>110</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18">
+        <v>15474</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18">
         <v>3</v>
       </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4">
-        <v>6.2500000000000001E-4</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="I18">
+        <v>7531</v>
+      </c>
+      <c r="J18">
+        <v>141</v>
+      </c>
+      <c r="K18">
+        <v>12</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>10</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="P18" s="4">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="R18" s="5">
+        <v>8.5099999999999995E-2</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>2</v>
+      </c>
+      <c r="U18" s="5">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="V18" s="5">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>12.787599999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19">
+        <v>71</v>
+      </c>
+      <c r="D19">
+        <v>110</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19">
+        <v>15474</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>4606</v>
+      </c>
+      <c r="J19">
+        <v>110</v>
+      </c>
+      <c r="K19">
+        <v>8</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>7</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19" s="4">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P19" s="4">
+        <v>2.1412037037037038E-3</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="R19" s="5">
+        <v>7.2700000000000001E-2</v>
+      </c>
+      <c r="S19" s="3">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="V19" s="5">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>16.6143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20">
+        <v>71</v>
+      </c>
+      <c r="D20">
+        <v>110</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20">
+        <v>15474</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>15658</v>
+      </c>
+      <c r="J20">
+        <v>326</v>
+      </c>
+      <c r="K20">
+        <v>14</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>11</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="P20" s="4">
+        <v>1.0532407407407407E-3</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="R20" s="5">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>3</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0.21429999999999999</v>
+      </c>
+      <c r="V20" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="W20">
+        <v>40.482199999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <v>71</v>
+      </c>
+      <c r="D21">
+        <v>110</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21">
+        <v>15474</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>4495</v>
+      </c>
+      <c r="J21">
+        <v>22</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4">
+        <v>2.3495370370370371E-3</v>
+      </c>
+      <c r="P21" s="4">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="R21" s="5">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="5">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>3.4914000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B22">
+        <v>17</v>
+      </c>
+      <c r="C22">
+        <v>71</v>
+      </c>
+      <c r="D22">
+        <v>110</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22">
+        <v>15474</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>4788</v>
+      </c>
+      <c r="J22">
+        <v>155</v>
+      </c>
+      <c r="K22">
+        <v>12</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>10</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" s="4">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="P22" s="4">
+        <v>8.7962962962962962E-4</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="R22" s="5">
+        <v>7.7399999999999997E-2</v>
+      </c>
+      <c r="S22" s="5">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22" s="5">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="V22" s="5">
+        <v>0.90910000000000002</v>
+      </c>
+      <c r="W22">
+        <v>12.0046</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B23">
+        <v>18</v>
+      </c>
+      <c r="C23">
+        <v>71</v>
+      </c>
+      <c r="D23">
+        <v>110</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23">
+        <v>15474</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>71</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="P23" t="s">
         <v>24</v>
       </c>
-      <c r="Q16" s="5">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="R16" s="5">
-        <v>5.5599999999999997E-2</v>
-      </c>
-      <c r="S16" s="3">
-        <v>1</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16" t="s">
-        <v>25</v>
-      </c>
-      <c r="V16" t="s">
-        <v>25</v>
-      </c>
-      <c r="W16">
-        <v>10.864000000000001</v>
+      <c r="Q23" s="5">
+        <v>1.41E-2</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23" t="s">
+        <v>25</v>
+      </c>
+      <c r="V23" t="s">
+        <v>25</v>
+      </c>
+      <c r="W23">
+        <v>6.2E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_setra.xlsx
+++ b/data/base_setra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2179B4E-291D-484F-9F51-CB10D4756E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0CBC09-E63C-4467-874C-59C6AB74356F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1999,19 +1999,19 @@
         <v>2</v>
       </c>
       <c r="I22">
-        <v>4788</v>
+        <v>4790</v>
       </c>
       <c r="J22">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K22">
         <v>12</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -2020,28 +2020,28 @@
         <v>3.4722222222222224E-4</v>
       </c>
       <c r="P22" s="4">
-        <v>8.7962962962962962E-4</v>
+        <v>8.3333333333333339E-4</v>
       </c>
       <c r="Q22" s="5">
-        <v>3.2399999999999998E-2</v>
+        <v>3.2800000000000003E-2</v>
       </c>
       <c r="R22" s="5">
-        <v>7.7399999999999997E-2</v>
+        <v>7.6399999999999996E-2</v>
       </c>
       <c r="S22" s="5">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22" s="5">
         <v>8.3299999999999999E-2</v>
       </c>
-      <c r="T22">
-        <v>1</v>
-      </c>
-      <c r="U22" s="5">
-        <v>9.0899999999999995E-2</v>
-      </c>
       <c r="V22" s="5">
-        <v>0.90910000000000002</v>
+        <v>0.91669999999999996</v>
       </c>
       <c r="W22">
-        <v>12.0046</v>
+        <v>12.0418</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -2064,16 +2064,16 @@
         <v>15474</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         <v>0</v>
       </c>
       <c r="O23" s="4">
-        <v>8.1018518518518516E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="P23" t="s">
         <v>24</v>
       </c>
       <c r="Q23" s="5">
-        <v>1.41E-2</v>
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="R23" s="3">
         <v>0</v>
@@ -2112,7 +2112,7 @@
         <v>25</v>
       </c>
       <c r="W23">
-        <v>6.2E-2</v>
+        <v>0.16950000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_setra.xlsx
+++ b/data/base_setra.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0CBC09-E63C-4467-874C-59C6AB74356F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8C7D59-8B50-4C42-84C7-D0F2B169C68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -2118,4 +2119,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8EC477-1B43-4018-A954-FC6335D35A68}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/base_setra.xlsx
+++ b/data/base_setra.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8C7D59-8B50-4C42-84C7-D0F2B169C68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8547EFD-946F-42E6-A19B-A71EEFBEC784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
+    <sheet name="Funil_3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -2128,4 +2129,13 @@
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6251127-DD8C-46CF-BC22-049BE7678644}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/base_setra.xlsx
+++ b/data/base_setra.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8547EFD-946F-42E6-A19B-A71EEFBEC784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5354CCC0-41D5-46F9-8940-D3CB554C2BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="27">
   <si>
     <t>Data</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>%</t>
+  </si>
+  <si>
+    <t>70 - Locator_Sem CPF</t>
   </si>
 </sst>
 </file>
@@ -471,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -2117,6 +2120,1772 @@
         <v>0.16950000000000001</v>
       </c>
     </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>70</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>4</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="P24" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" t="s">
+        <v>25</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" t="s">
+        <v>25</v>
+      </c>
+      <c r="W24">
+        <v>7.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>71</v>
+      </c>
+      <c r="D25">
+        <v>110</v>
+      </c>
+      <c r="E25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25">
+        <v>15474</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>4210</v>
+      </c>
+      <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
+        <v>3</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>3</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" s="4">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P25" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="5">
+        <v>1</v>
+      </c>
+      <c r="W25">
+        <v>11.6624</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B26">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <v>70</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>8</v>
+      </c>
+      <c r="J26">
+        <v>5</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P26" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="S26" s="3">
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26" t="s">
+        <v>25</v>
+      </c>
+      <c r="W26">
+        <v>0.1085</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27">
+        <v>71</v>
+      </c>
+      <c r="D27">
+        <v>110</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27">
+        <v>15474</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>12343</v>
+      </c>
+      <c r="J27">
+        <v>315</v>
+      </c>
+      <c r="K27">
+        <v>15</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>13</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P27" s="4">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="R27" s="5">
+        <v>4.7600000000000003E-2</v>
+      </c>
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>2</v>
+      </c>
+      <c r="U27" s="5">
+        <v>0.1333</v>
+      </c>
+      <c r="V27" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="W27">
+        <v>32.084600000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>71</v>
+      </c>
+      <c r="D28">
+        <v>110</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28">
+        <v>15474</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <v>15323</v>
+      </c>
+      <c r="J28">
+        <v>343</v>
+      </c>
+      <c r="K28">
+        <v>18</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>17</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" s="4">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="P28" s="4">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>2.24E-2</v>
+      </c>
+      <c r="R28" s="5">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28" s="5">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="V28" s="5">
+        <v>1</v>
+      </c>
+      <c r="W28">
+        <v>33.525300000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+      <c r="C29">
+        <v>71</v>
+      </c>
+      <c r="D29">
+        <v>110</v>
+      </c>
+      <c r="E29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29">
+        <v>15474</v>
+      </c>
+      <c r="G29">
+        <v>10</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>14705</v>
+      </c>
+      <c r="J29">
+        <v>255</v>
+      </c>
+      <c r="K29">
+        <v>9</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>9</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" s="4">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="P29" s="4">
+        <v>9.2592592592592596E-4</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="R29" s="5">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="5">
+        <v>0.88890000000000002</v>
+      </c>
+      <c r="W29">
+        <v>27.486799999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30">
+        <v>71</v>
+      </c>
+      <c r="D30">
+        <v>110</v>
+      </c>
+      <c r="E30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30">
+        <v>15474</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>6422</v>
+      </c>
+      <c r="J30">
+        <v>81</v>
+      </c>
+      <c r="K30">
+        <v>7</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>5</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" s="4">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="P30" s="4">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>1.26E-2</v>
+      </c>
+      <c r="R30" s="5">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>2</v>
+      </c>
+      <c r="U30" s="5">
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="V30" s="5">
+        <v>1</v>
+      </c>
+      <c r="W30">
+        <v>12.5589</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31">
+        <v>71</v>
+      </c>
+      <c r="D31">
+        <v>110</v>
+      </c>
+      <c r="E31" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31">
+        <v>15474</v>
+      </c>
+      <c r="G31">
+        <v>10</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>8577</v>
+      </c>
+      <c r="J31">
+        <v>122</v>
+      </c>
+      <c r="K31">
+        <v>6</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="P31" s="4">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="Q31" s="5">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="R31" s="5">
+        <v>4.9200000000000001E-2</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>2</v>
+      </c>
+      <c r="U31" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="V31" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="W31">
+        <v>20.348199999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B32">
+        <v>16</v>
+      </c>
+      <c r="C32">
+        <v>71</v>
+      </c>
+      <c r="D32">
+        <v>110</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32">
+        <v>15474</v>
+      </c>
+      <c r="G32">
+        <v>10</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
+      </c>
+      <c r="I32">
+        <v>5658</v>
+      </c>
+      <c r="J32">
+        <v>116</v>
+      </c>
+      <c r="K32">
+        <v>4</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>4</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" s="4">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="P32" s="4">
+        <v>1.8402777777777777E-3</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="R32" s="5">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="W32">
+        <v>12.520300000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B33">
+        <v>17</v>
+      </c>
+      <c r="C33">
+        <v>71</v>
+      </c>
+      <c r="D33">
+        <v>110</v>
+      </c>
+      <c r="E33" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33">
+        <v>15474</v>
+      </c>
+      <c r="G33">
+        <v>10</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <v>5928</v>
+      </c>
+      <c r="J33">
+        <v>192</v>
+      </c>
+      <c r="K33">
+        <v>8</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>8</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" s="4">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="P33" s="4">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="Q33" s="5">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="R33" s="5">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="5">
+        <v>1</v>
+      </c>
+      <c r="W33">
+        <v>10.2986</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B34">
+        <v>18</v>
+      </c>
+      <c r="C34">
+        <v>71</v>
+      </c>
+      <c r="D34">
+        <v>110</v>
+      </c>
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34">
+        <v>15474</v>
+      </c>
+      <c r="G34">
+        <v>10</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>1133</v>
+      </c>
+      <c r="J34">
+        <v>27</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" s="4">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P34" s="4">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="R34" s="5">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="5">
+        <v>1</v>
+      </c>
+      <c r="W34">
+        <v>1.595</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>71</v>
+      </c>
+      <c r="D35">
+        <v>110</v>
+      </c>
+      <c r="E35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35">
+        <v>17310</v>
+      </c>
+      <c r="G35">
+        <v>10</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>14212</v>
+      </c>
+      <c r="J35">
+        <v>446</v>
+      </c>
+      <c r="K35">
+        <v>18</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>15</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" s="4">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="P35" s="4">
+        <v>1.0532407407407407E-3</v>
+      </c>
+      <c r="Q35" s="5">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="R35" s="5">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>3</v>
+      </c>
+      <c r="U35" s="5">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="V35" s="5">
+        <v>0.95240000000000002</v>
+      </c>
+      <c r="W35">
+        <v>28.329599999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+      <c r="C36">
+        <v>71</v>
+      </c>
+      <c r="D36">
+        <v>110</v>
+      </c>
+      <c r="E36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36">
+        <v>17310</v>
+      </c>
+      <c r="G36">
+        <v>10</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>3637</v>
+      </c>
+      <c r="J36">
+        <v>33</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>2</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" s="4">
+        <v>1.2731481481481483E-3</v>
+      </c>
+      <c r="P36" s="4">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="R36" s="5">
+        <v>6.0600000000000001E-2</v>
+      </c>
+      <c r="S36" s="3">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36" s="3">
+        <v>0</v>
+      </c>
+      <c r="V36" s="5">
+        <v>1</v>
+      </c>
+      <c r="W36">
+        <v>4.4297000000000004</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>71</v>
+      </c>
+      <c r="D37">
+        <v>110</v>
+      </c>
+      <c r="E37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37">
+        <v>17310</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37">
+        <v>13452</v>
+      </c>
+      <c r="J37">
+        <v>326</v>
+      </c>
+      <c r="K37">
+        <v>23</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>17</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="P37" s="4">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>2.4199999999999999E-2</v>
+      </c>
+      <c r="R37" s="5">
+        <v>7.0599999999999996E-2</v>
+      </c>
+      <c r="S37" s="3">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>6</v>
+      </c>
+      <c r="U37" s="5">
+        <v>0.26090000000000002</v>
+      </c>
+      <c r="V37" s="5">
+        <v>0.77780000000000005</v>
+      </c>
+      <c r="W37">
+        <v>35.240699999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B38">
+        <v>11</v>
+      </c>
+      <c r="C38">
+        <v>71</v>
+      </c>
+      <c r="D38">
+        <v>110</v>
+      </c>
+      <c r="E38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38">
+        <v>17310</v>
+      </c>
+      <c r="G38">
+        <v>10</v>
+      </c>
+      <c r="H38">
+        <v>5</v>
+      </c>
+      <c r="I38">
+        <v>20691</v>
+      </c>
+      <c r="J38">
+        <v>424</v>
+      </c>
+      <c r="K38">
+        <v>27</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>24</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" s="4">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="P38" s="4">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="R38" s="5">
+        <v>6.3700000000000007E-2</v>
+      </c>
+      <c r="S38" s="5">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="T38">
+        <v>2</v>
+      </c>
+      <c r="U38" s="5">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="V38" s="5">
+        <v>0.86209999999999998</v>
+      </c>
+      <c r="W38">
+        <v>48.917400000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B39">
+        <v>12</v>
+      </c>
+      <c r="C39">
+        <v>71</v>
+      </c>
+      <c r="D39">
+        <v>110</v>
+      </c>
+      <c r="E39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39">
+        <v>17310</v>
+      </c>
+      <c r="G39">
+        <v>10</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39">
+        <v>10627</v>
+      </c>
+      <c r="J39">
+        <v>263</v>
+      </c>
+      <c r="K39">
+        <v>17</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>14</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" s="4">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P39" s="4">
+        <v>1.6782407407407408E-3</v>
+      </c>
+      <c r="Q39" s="5">
+        <v>2.47E-2</v>
+      </c>
+      <c r="R39" s="5">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="S39" s="3">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>3</v>
+      </c>
+      <c r="U39" s="5">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="V39" s="5">
+        <v>0.71430000000000005</v>
+      </c>
+      <c r="W39">
+        <v>24.250900000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B40">
+        <v>13</v>
+      </c>
+      <c r="C40">
+        <v>71</v>
+      </c>
+      <c r="D40">
+        <v>110</v>
+      </c>
+      <c r="E40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40">
+        <v>17310</v>
+      </c>
+      <c r="G40">
+        <v>10</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>2656</v>
+      </c>
+      <c r="J40">
+        <v>31</v>
+      </c>
+      <c r="K40">
+        <v>2</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" s="4">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="P40" s="4">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="Q40" s="5">
+        <v>1.17E-2</v>
+      </c>
+      <c r="R40" s="5">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="S40" s="3">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
+      </c>
+      <c r="U40" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V40" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="W40">
+        <v>2.5842000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B41">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>71</v>
+      </c>
+      <c r="D41">
+        <v>110</v>
+      </c>
+      <c r="E41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41">
+        <v>14693</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+      <c r="I41">
+        <v>16508</v>
+      </c>
+      <c r="J41">
+        <v>609</v>
+      </c>
+      <c r="K41">
+        <v>30</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>25</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" s="4">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="P41" s="4">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="Q41" s="5">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="R41" s="5">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>5</v>
+      </c>
+      <c r="U41" s="5">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="V41" s="5">
+        <v>0.84379999999999999</v>
+      </c>
+      <c r="W41">
+        <v>35.328099999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B42">
+        <v>9</v>
+      </c>
+      <c r="C42">
+        <v>71</v>
+      </c>
+      <c r="D42">
+        <v>110</v>
+      </c>
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42">
+        <v>14693</v>
+      </c>
+      <c r="G42">
+        <v>10</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+      <c r="I42">
+        <v>3599</v>
+      </c>
+      <c r="J42">
+        <v>29</v>
+      </c>
+      <c r="K42">
+        <v>2</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>2</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" s="4">
+        <v>1.4236111111111112E-3</v>
+      </c>
+      <c r="P42" s="4">
+        <v>1.0069444444444444E-3</v>
+      </c>
+      <c r="Q42" s="5">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="R42" s="5">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="5">
+        <v>1</v>
+      </c>
+      <c r="W42">
+        <v>5.0456000000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B43">
+        <v>10</v>
+      </c>
+      <c r="C43">
+        <v>71</v>
+      </c>
+      <c r="D43">
+        <v>110</v>
+      </c>
+      <c r="E43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43">
+        <v>14693</v>
+      </c>
+      <c r="G43">
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>3</v>
+      </c>
+      <c r="I43">
+        <v>17550</v>
+      </c>
+      <c r="J43">
+        <v>327</v>
+      </c>
+      <c r="K43">
+        <v>4</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>4</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" s="4">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="P43" s="4">
+        <v>1.2037037037037038E-3</v>
+      </c>
+      <c r="Q43" s="5">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="R43" s="5">
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="5">
+        <v>1</v>
+      </c>
+      <c r="W43">
+        <v>55.8245</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B44">
+        <v>11</v>
+      </c>
+      <c r="C44">
+        <v>71</v>
+      </c>
+      <c r="D44">
+        <v>110</v>
+      </c>
+      <c r="E44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44">
+        <v>14693</v>
+      </c>
+      <c r="G44">
+        <v>10</v>
+      </c>
+      <c r="H44">
+        <v>3</v>
+      </c>
+      <c r="I44">
+        <v>21427</v>
+      </c>
+      <c r="J44">
+        <v>330</v>
+      </c>
+      <c r="K44">
+        <v>7</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>6</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" s="4">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="P44" s="4">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>1.54E-2</v>
+      </c>
+      <c r="R44" s="5">
+        <v>2.12E-2</v>
+      </c>
+      <c r="S44" s="5">
+        <v>0.1429</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="5">
+        <v>1</v>
+      </c>
+      <c r="W44">
+        <v>64.881299999999996</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B45">
+        <v>12</v>
+      </c>
+      <c r="C45">
+        <v>71</v>
+      </c>
+      <c r="D45">
+        <v>110</v>
+      </c>
+      <c r="E45" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45">
+        <v>14693</v>
+      </c>
+      <c r="G45">
+        <v>10</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+      <c r="I45">
+        <v>14310</v>
+      </c>
+      <c r="J45">
+        <v>323</v>
+      </c>
+      <c r="K45">
+        <v>7</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>7</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" s="4">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P45" s="4">
+        <v>1.0300925925925926E-3</v>
+      </c>
+      <c r="Q45" s="5">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="R45" s="5">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="5">
+        <v>1</v>
+      </c>
+      <c r="W45">
+        <v>42.174500000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B46">
+        <v>13</v>
+      </c>
+      <c r="C46">
+        <v>71</v>
+      </c>
+      <c r="D46">
+        <v>110</v>
+      </c>
+      <c r="E46" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46">
+        <v>14693</v>
+      </c>
+      <c r="G46">
+        <v>10</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>1704</v>
+      </c>
+      <c r="J46">
+        <v>17</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" s="4">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="P46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" t="s">
+        <v>25</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46" t="s">
+        <v>25</v>
+      </c>
+      <c r="V46" t="s">
+        <v>25</v>
+      </c>
+      <c r="W46">
+        <v>2.1067999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B47">
+        <v>15</v>
+      </c>
+      <c r="C47">
+        <v>70</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P47" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>1</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" t="s">
+        <v>25</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47" t="s">
+        <v>25</v>
+      </c>
+      <c r="W47">
+        <v>4.3400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B48">
+        <v>15</v>
+      </c>
+      <c r="C48">
+        <v>71</v>
+      </c>
+      <c r="D48">
+        <v>110</v>
+      </c>
+      <c r="E48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48">
+        <v>14693</v>
+      </c>
+      <c r="G48">
+        <v>10</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+      <c r="I48">
+        <v>7644</v>
+      </c>
+      <c r="J48">
+        <v>185</v>
+      </c>
+      <c r="K48">
+        <v>12</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>10</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" s="4">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P48" s="4">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="Q48" s="5">
+        <v>2.4199999999999999E-2</v>
+      </c>
+      <c r="R48" s="5">
+        <v>6.4899999999999999E-2</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>2</v>
+      </c>
+      <c r="U48" s="5">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="V48" s="5">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="W48">
+        <v>28.229600000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/base_setra.xlsx
+++ b/data/base_setra.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5354CCC0-41D5-46F9-8940-D3CB554C2BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8547EFD-946F-42E6-A19B-A71EEFBEC784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>%</t>
-  </si>
-  <si>
-    <t>70 - Locator_Sem CPF</t>
   </si>
 </sst>
 </file>
@@ -474,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -2120,1772 +2117,6 @@
         <v>0.16950000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B24">
-        <v>10</v>
-      </c>
-      <c r="C24">
-        <v>70</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>4</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" s="4">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="P24" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" t="s">
-        <v>25</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24" t="s">
-        <v>25</v>
-      </c>
-      <c r="W24">
-        <v>7.7499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B25">
-        <v>10</v>
-      </c>
-      <c r="C25">
-        <v>71</v>
-      </c>
-      <c r="D25">
-        <v>110</v>
-      </c>
-      <c r="E25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25">
-        <v>15474</v>
-      </c>
-      <c r="G25">
-        <v>10</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>4210</v>
-      </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
-      <c r="K25">
-        <v>3</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>3</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" s="4">
-        <v>4.7453703703703704E-4</v>
-      </c>
-      <c r="P25" s="4">
-        <v>2.199074074074074E-4</v>
-      </c>
-      <c r="Q25" s="5">
-        <v>2.3800000000000002E-2</v>
-      </c>
-      <c r="R25" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="S25" s="3">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25" s="3">
-        <v>0</v>
-      </c>
-      <c r="V25" s="5">
-        <v>1</v>
-      </c>
-      <c r="W25">
-        <v>11.6624</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B26">
-        <v>11</v>
-      </c>
-      <c r="C26">
-        <v>70</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>8</v>
-      </c>
-      <c r="J26">
-        <v>5</v>
-      </c>
-      <c r="K26">
-        <v>2</v>
-      </c>
-      <c r="L26">
-        <v>2</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="P26" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q26" s="5">
-        <v>0.625</v>
-      </c>
-      <c r="R26" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="S26" s="3">
-        <v>1</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26" t="s">
-        <v>25</v>
-      </c>
-      <c r="W26">
-        <v>0.1085</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B27">
-        <v>11</v>
-      </c>
-      <c r="C27">
-        <v>71</v>
-      </c>
-      <c r="D27">
-        <v>110</v>
-      </c>
-      <c r="E27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27">
-        <v>15474</v>
-      </c>
-      <c r="G27">
-        <v>10</v>
-      </c>
-      <c r="H27">
-        <v>3</v>
-      </c>
-      <c r="I27">
-        <v>12343</v>
-      </c>
-      <c r="J27">
-        <v>315</v>
-      </c>
-      <c r="K27">
-        <v>15</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>13</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" s="4">
-        <v>4.5138888888888887E-4</v>
-      </c>
-      <c r="P27" s="4">
-        <v>5.2083333333333333E-4</v>
-      </c>
-      <c r="Q27" s="5">
-        <v>2.5499999999999998E-2</v>
-      </c>
-      <c r="R27" s="5">
-        <v>4.7600000000000003E-2</v>
-      </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>2</v>
-      </c>
-      <c r="U27" s="5">
-        <v>0.1333</v>
-      </c>
-      <c r="V27" s="5">
-        <v>0.9375</v>
-      </c>
-      <c r="W27">
-        <v>32.084600000000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B28">
-        <v>12</v>
-      </c>
-      <c r="C28">
-        <v>71</v>
-      </c>
-      <c r="D28">
-        <v>110</v>
-      </c>
-      <c r="E28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28">
-        <v>15474</v>
-      </c>
-      <c r="G28">
-        <v>10</v>
-      </c>
-      <c r="H28">
-        <v>2</v>
-      </c>
-      <c r="I28">
-        <v>15323</v>
-      </c>
-      <c r="J28">
-        <v>343</v>
-      </c>
-      <c r="K28">
-        <v>18</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>17</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" s="4">
-        <v>5.0925925925925921E-4</v>
-      </c>
-      <c r="P28" s="4">
-        <v>6.5972222222222224E-4</v>
-      </c>
-      <c r="Q28" s="5">
-        <v>2.24E-2</v>
-      </c>
-      <c r="R28" s="5">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="S28" s="3">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>1</v>
-      </c>
-      <c r="U28" s="5">
-        <v>5.5599999999999997E-2</v>
-      </c>
-      <c r="V28" s="5">
-        <v>1</v>
-      </c>
-      <c r="W28">
-        <v>33.525300000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B29">
-        <v>13</v>
-      </c>
-      <c r="C29">
-        <v>71</v>
-      </c>
-      <c r="D29">
-        <v>110</v>
-      </c>
-      <c r="E29" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29">
-        <v>15474</v>
-      </c>
-      <c r="G29">
-        <v>10</v>
-      </c>
-      <c r="H29">
-        <v>2</v>
-      </c>
-      <c r="I29">
-        <v>14705</v>
-      </c>
-      <c r="J29">
-        <v>255</v>
-      </c>
-      <c r="K29">
-        <v>9</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>9</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" s="4">
-        <v>6.5972222222222224E-4</v>
-      </c>
-      <c r="P29" s="4">
-        <v>9.2592592592592596E-4</v>
-      </c>
-      <c r="Q29" s="5">
-        <v>1.7299999999999999E-2</v>
-      </c>
-      <c r="R29" s="5">
-        <v>3.5299999999999998E-2</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="5">
-        <v>0.88890000000000002</v>
-      </c>
-      <c r="W29">
-        <v>27.486799999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B30">
-        <v>14</v>
-      </c>
-      <c r="C30">
-        <v>71</v>
-      </c>
-      <c r="D30">
-        <v>110</v>
-      </c>
-      <c r="E30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30">
-        <v>15474</v>
-      </c>
-      <c r="G30">
-        <v>10</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>6422</v>
-      </c>
-      <c r="J30">
-        <v>81</v>
-      </c>
-      <c r="K30">
-        <v>7</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>5</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" s="4">
-        <v>9.0277777777777774E-4</v>
-      </c>
-      <c r="P30" s="4">
-        <v>8.6805555555555551E-4</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>1.26E-2</v>
-      </c>
-      <c r="R30" s="5">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S30" s="3">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>2</v>
-      </c>
-      <c r="U30" s="5">
-        <v>0.28570000000000001</v>
-      </c>
-      <c r="V30" s="5">
-        <v>1</v>
-      </c>
-      <c r="W30">
-        <v>12.5589</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B31">
-        <v>15</v>
-      </c>
-      <c r="C31">
-        <v>71</v>
-      </c>
-      <c r="D31">
-        <v>110</v>
-      </c>
-      <c r="E31" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31">
-        <v>15474</v>
-      </c>
-      <c r="G31">
-        <v>10</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="I31">
-        <v>8577</v>
-      </c>
-      <c r="J31">
-        <v>122</v>
-      </c>
-      <c r="K31">
-        <v>6</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>4</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" s="4">
-        <v>8.1018518518518516E-4</v>
-      </c>
-      <c r="P31" s="4">
-        <v>8.6805555555555551E-4</v>
-      </c>
-      <c r="Q31" s="5">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="R31" s="5">
-        <v>4.9200000000000001E-2</v>
-      </c>
-      <c r="S31" s="3">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>2</v>
-      </c>
-      <c r="U31" s="5">
-        <v>0.33329999999999999</v>
-      </c>
-      <c r="V31" s="5">
-        <v>0.625</v>
-      </c>
-      <c r="W31">
-        <v>20.348199999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B32">
-        <v>16</v>
-      </c>
-      <c r="C32">
-        <v>71</v>
-      </c>
-      <c r="D32">
-        <v>110</v>
-      </c>
-      <c r="E32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32">
-        <v>15474</v>
-      </c>
-      <c r="G32">
-        <v>10</v>
-      </c>
-      <c r="H32">
-        <v>2</v>
-      </c>
-      <c r="I32">
-        <v>5658</v>
-      </c>
-      <c r="J32">
-        <v>116</v>
-      </c>
-      <c r="K32">
-        <v>4</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>4</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" s="4">
-        <v>5.5555555555555556E-4</v>
-      </c>
-      <c r="P32" s="4">
-        <v>1.8402777777777777E-3</v>
-      </c>
-      <c r="Q32" s="5">
-        <v>2.0500000000000001E-2</v>
-      </c>
-      <c r="R32" s="5">
-        <v>3.4500000000000003E-2</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="W32">
-        <v>12.520300000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B33">
-        <v>17</v>
-      </c>
-      <c r="C33">
-        <v>71</v>
-      </c>
-      <c r="D33">
-        <v>110</v>
-      </c>
-      <c r="E33" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33">
-        <v>15474</v>
-      </c>
-      <c r="G33">
-        <v>10</v>
-      </c>
-      <c r="H33">
-        <v>2</v>
-      </c>
-      <c r="I33">
-        <v>5928</v>
-      </c>
-      <c r="J33">
-        <v>192</v>
-      </c>
-      <c r="K33">
-        <v>8</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>8</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33" s="4">
-        <v>3.4722222222222224E-4</v>
-      </c>
-      <c r="P33" s="4">
-        <v>4.1666666666666669E-4</v>
-      </c>
-      <c r="Q33" s="5">
-        <v>3.2399999999999998E-2</v>
-      </c>
-      <c r="R33" s="5">
-        <v>4.1700000000000001E-2</v>
-      </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="5">
-        <v>1</v>
-      </c>
-      <c r="W33">
-        <v>10.2986</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>46183</v>
-      </c>
-      <c r="B34">
-        <v>18</v>
-      </c>
-      <c r="C34">
-        <v>71</v>
-      </c>
-      <c r="D34">
-        <v>110</v>
-      </c>
-      <c r="E34" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34">
-        <v>15474</v>
-      </c>
-      <c r="G34">
-        <v>10</v>
-      </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="I34">
-        <v>1133</v>
-      </c>
-      <c r="J34">
-        <v>27</v>
-      </c>
-      <c r="K34">
-        <v>1</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34" s="4">
-        <v>4.7453703703703704E-4</v>
-      </c>
-      <c r="P34" s="4">
-        <v>4.2824074074074075E-4</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>2.3800000000000002E-2</v>
-      </c>
-      <c r="R34" s="5">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="S34" s="3">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34" s="3">
-        <v>0</v>
-      </c>
-      <c r="V34" s="5">
-        <v>1</v>
-      </c>
-      <c r="W34">
-        <v>1.595</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>46184</v>
-      </c>
-      <c r="B35">
-        <v>8</v>
-      </c>
-      <c r="C35">
-        <v>71</v>
-      </c>
-      <c r="D35">
-        <v>110</v>
-      </c>
-      <c r="E35" t="s">
-        <v>23</v>
-      </c>
-      <c r="F35">
-        <v>17310</v>
-      </c>
-      <c r="G35">
-        <v>10</v>
-      </c>
-      <c r="H35">
-        <v>2</v>
-      </c>
-      <c r="I35">
-        <v>14212</v>
-      </c>
-      <c r="J35">
-        <v>446</v>
-      </c>
-      <c r="K35">
-        <v>18</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>15</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35" s="4">
-        <v>3.5879629629629629E-4</v>
-      </c>
-      <c r="P35" s="4">
-        <v>1.0532407407407407E-3</v>
-      </c>
-      <c r="Q35" s="5">
-        <v>3.1399999999999997E-2</v>
-      </c>
-      <c r="R35" s="5">
-        <v>4.0399999999999998E-2</v>
-      </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>3</v>
-      </c>
-      <c r="U35" s="5">
-        <v>0.16669999999999999</v>
-      </c>
-      <c r="V35" s="5">
-        <v>0.95240000000000002</v>
-      </c>
-      <c r="W35">
-        <v>28.329599999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>46184</v>
-      </c>
-      <c r="B36">
-        <v>9</v>
-      </c>
-      <c r="C36">
-        <v>71</v>
-      </c>
-      <c r="D36">
-        <v>110</v>
-      </c>
-      <c r="E36" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36">
-        <v>17310</v>
-      </c>
-      <c r="G36">
-        <v>10</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
-        <v>3637</v>
-      </c>
-      <c r="J36">
-        <v>33</v>
-      </c>
-      <c r="K36">
-        <v>2</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>2</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36" s="4">
-        <v>1.2731481481481483E-3</v>
-      </c>
-      <c r="P36" s="4">
-        <v>4.5138888888888887E-4</v>
-      </c>
-      <c r="Q36" s="5">
-        <v>9.1000000000000004E-3</v>
-      </c>
-      <c r="R36" s="5">
-        <v>6.0600000000000001E-2</v>
-      </c>
-      <c r="S36" s="3">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36" s="3">
-        <v>0</v>
-      </c>
-      <c r="V36" s="5">
-        <v>1</v>
-      </c>
-      <c r="W36">
-        <v>4.4297000000000004</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
-        <v>46184</v>
-      </c>
-      <c r="B37">
-        <v>10</v>
-      </c>
-      <c r="C37">
-        <v>71</v>
-      </c>
-      <c r="D37">
-        <v>110</v>
-      </c>
-      <c r="E37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F37">
-        <v>17310</v>
-      </c>
-      <c r="G37">
-        <v>10</v>
-      </c>
-      <c r="H37">
-        <v>3</v>
-      </c>
-      <c r="I37">
-        <v>13452</v>
-      </c>
-      <c r="J37">
-        <v>326</v>
-      </c>
-      <c r="K37">
-        <v>23</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>17</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37" s="4">
-        <v>4.3981481481481481E-4</v>
-      </c>
-      <c r="P37" s="4">
-        <v>1.2268518518518518E-3</v>
-      </c>
-      <c r="Q37" s="5">
-        <v>2.4199999999999999E-2</v>
-      </c>
-      <c r="R37" s="5">
-        <v>7.0599999999999996E-2</v>
-      </c>
-      <c r="S37" s="3">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>6</v>
-      </c>
-      <c r="U37" s="5">
-        <v>0.26090000000000002</v>
-      </c>
-      <c r="V37" s="5">
-        <v>0.77780000000000005</v>
-      </c>
-      <c r="W37">
-        <v>35.240699999999997</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
-        <v>46184</v>
-      </c>
-      <c r="B38">
-        <v>11</v>
-      </c>
-      <c r="C38">
-        <v>71</v>
-      </c>
-      <c r="D38">
-        <v>110</v>
-      </c>
-      <c r="E38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F38">
-        <v>17310</v>
-      </c>
-      <c r="G38">
-        <v>10</v>
-      </c>
-      <c r="H38">
-        <v>5</v>
-      </c>
-      <c r="I38">
-        <v>20691</v>
-      </c>
-      <c r="J38">
-        <v>424</v>
-      </c>
-      <c r="K38">
-        <v>27</v>
-      </c>
-      <c r="L38">
-        <v>1</v>
-      </c>
-      <c r="M38">
-        <v>24</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38" s="4">
-        <v>5.3240740740740744E-4</v>
-      </c>
-      <c r="P38" s="4">
-        <v>8.1018518518518516E-4</v>
-      </c>
-      <c r="Q38" s="5">
-        <v>2.0500000000000001E-2</v>
-      </c>
-      <c r="R38" s="5">
-        <v>6.3700000000000007E-2</v>
-      </c>
-      <c r="S38" s="5">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="T38">
-        <v>2</v>
-      </c>
-      <c r="U38" s="5">
-        <v>7.6899999999999996E-2</v>
-      </c>
-      <c r="V38" s="5">
-        <v>0.86209999999999998</v>
-      </c>
-      <c r="W38">
-        <v>48.917400000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
-        <v>46184</v>
-      </c>
-      <c r="B39">
-        <v>12</v>
-      </c>
-      <c r="C39">
-        <v>71</v>
-      </c>
-      <c r="D39">
-        <v>110</v>
-      </c>
-      <c r="E39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F39">
-        <v>17310</v>
-      </c>
-      <c r="G39">
-        <v>10</v>
-      </c>
-      <c r="H39">
-        <v>3</v>
-      </c>
-      <c r="I39">
-        <v>10627</v>
-      </c>
-      <c r="J39">
-        <v>263</v>
-      </c>
-      <c r="K39">
-        <v>17</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>14</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39" s="4">
-        <v>4.6296296296296298E-4</v>
-      </c>
-      <c r="P39" s="4">
-        <v>1.6782407407407408E-3</v>
-      </c>
-      <c r="Q39" s="5">
-        <v>2.47E-2</v>
-      </c>
-      <c r="R39" s="5">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="S39" s="3">
-        <v>0</v>
-      </c>
-      <c r="T39">
-        <v>3</v>
-      </c>
-      <c r="U39" s="5">
-        <v>0.17649999999999999</v>
-      </c>
-      <c r="V39" s="5">
-        <v>0.71430000000000005</v>
-      </c>
-      <c r="W39">
-        <v>24.250900000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>46184</v>
-      </c>
-      <c r="B40">
-        <v>13</v>
-      </c>
-      <c r="C40">
-        <v>71</v>
-      </c>
-      <c r="D40">
-        <v>110</v>
-      </c>
-      <c r="E40" t="s">
-        <v>23</v>
-      </c>
-      <c r="F40">
-        <v>17310</v>
-      </c>
-      <c r="G40">
-        <v>10</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40">
-        <v>2656</v>
-      </c>
-      <c r="J40">
-        <v>31</v>
-      </c>
-      <c r="K40">
-        <v>2</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40" s="4">
-        <v>9.837962962962962E-4</v>
-      </c>
-      <c r="P40" s="4">
-        <v>9.837962962962962E-4</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>1.17E-2</v>
-      </c>
-      <c r="R40" s="5">
-        <v>6.4500000000000002E-2</v>
-      </c>
-      <c r="S40" s="3">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>1</v>
-      </c>
-      <c r="U40" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="V40" s="5">
-        <v>0.66669999999999996</v>
-      </c>
-      <c r="W40">
-        <v>2.5842000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B41">
-        <v>8</v>
-      </c>
-      <c r="C41">
-        <v>71</v>
-      </c>
-      <c r="D41">
-        <v>110</v>
-      </c>
-      <c r="E41" t="s">
-        <v>23</v>
-      </c>
-      <c r="F41">
-        <v>14693</v>
-      </c>
-      <c r="G41">
-        <v>10</v>
-      </c>
-      <c r="H41">
-        <v>3</v>
-      </c>
-      <c r="I41">
-        <v>16508</v>
-      </c>
-      <c r="J41">
-        <v>609</v>
-      </c>
-      <c r="K41">
-        <v>30</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>25</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41" s="4">
-        <v>3.0092592592592595E-4</v>
-      </c>
-      <c r="P41" s="4">
-        <v>9.837962962962962E-4</v>
-      </c>
-      <c r="Q41" s="5">
-        <v>3.6900000000000002E-2</v>
-      </c>
-      <c r="R41" s="5">
-        <v>4.9299999999999997E-2</v>
-      </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <v>5</v>
-      </c>
-      <c r="U41" s="5">
-        <v>0.16669999999999999</v>
-      </c>
-      <c r="V41" s="5">
-        <v>0.84379999999999999</v>
-      </c>
-      <c r="W41">
-        <v>35.328099999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B42">
-        <v>9</v>
-      </c>
-      <c r="C42">
-        <v>71</v>
-      </c>
-      <c r="D42">
-        <v>110</v>
-      </c>
-      <c r="E42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F42">
-        <v>14693</v>
-      </c>
-      <c r="G42">
-        <v>10</v>
-      </c>
-      <c r="H42">
-        <v>2</v>
-      </c>
-      <c r="I42">
-        <v>3599</v>
-      </c>
-      <c r="J42">
-        <v>29</v>
-      </c>
-      <c r="K42">
-        <v>2</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>2</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42" s="4">
-        <v>1.4236111111111112E-3</v>
-      </c>
-      <c r="P42" s="4">
-        <v>1.0069444444444444E-3</v>
-      </c>
-      <c r="Q42" s="5">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="R42" s="5">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-      <c r="V42" s="5">
-        <v>1</v>
-      </c>
-      <c r="W42">
-        <v>5.0456000000000003</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B43">
-        <v>10</v>
-      </c>
-      <c r="C43">
-        <v>71</v>
-      </c>
-      <c r="D43">
-        <v>110</v>
-      </c>
-      <c r="E43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F43">
-        <v>14693</v>
-      </c>
-      <c r="G43">
-        <v>10</v>
-      </c>
-      <c r="H43">
-        <v>3</v>
-      </c>
-      <c r="I43">
-        <v>17550</v>
-      </c>
-      <c r="J43">
-        <v>327</v>
-      </c>
-      <c r="K43">
-        <v>4</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>4</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43" s="4">
-        <v>6.134259259259259E-4</v>
-      </c>
-      <c r="P43" s="4">
-        <v>1.2037037037037038E-3</v>
-      </c>
-      <c r="Q43" s="5">
-        <v>1.8599999999999998E-2</v>
-      </c>
-      <c r="R43" s="5">
-        <v>1.2200000000000001E-2</v>
-      </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="5">
-        <v>1</v>
-      </c>
-      <c r="W43">
-        <v>55.8245</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B44">
-        <v>11</v>
-      </c>
-      <c r="C44">
-        <v>71</v>
-      </c>
-      <c r="D44">
-        <v>110</v>
-      </c>
-      <c r="E44" t="s">
-        <v>23</v>
-      </c>
-      <c r="F44">
-        <v>14693</v>
-      </c>
-      <c r="G44">
-        <v>10</v>
-      </c>
-      <c r="H44">
-        <v>3</v>
-      </c>
-      <c r="I44">
-        <v>21427</v>
-      </c>
-      <c r="J44">
-        <v>330</v>
-      </c>
-      <c r="K44">
-        <v>7</v>
-      </c>
-      <c r="L44">
-        <v>1</v>
-      </c>
-      <c r="M44">
-        <v>6</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44" s="4">
-        <v>7.291666666666667E-4</v>
-      </c>
-      <c r="P44" s="4">
-        <v>8.564814814814815E-4</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>1.54E-2</v>
-      </c>
-      <c r="R44" s="5">
-        <v>2.12E-2</v>
-      </c>
-      <c r="S44" s="5">
-        <v>0.1429</v>
-      </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3">
-        <v>0</v>
-      </c>
-      <c r="V44" s="5">
-        <v>1</v>
-      </c>
-      <c r="W44">
-        <v>64.881299999999996</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B45">
-        <v>12</v>
-      </c>
-      <c r="C45">
-        <v>71</v>
-      </c>
-      <c r="D45">
-        <v>110</v>
-      </c>
-      <c r="E45" t="s">
-        <v>23</v>
-      </c>
-      <c r="F45">
-        <v>14693</v>
-      </c>
-      <c r="G45">
-        <v>10</v>
-      </c>
-      <c r="H45">
-        <v>2</v>
-      </c>
-      <c r="I45">
-        <v>14310</v>
-      </c>
-      <c r="J45">
-        <v>323</v>
-      </c>
-      <c r="K45">
-        <v>7</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>7</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45" s="4">
-        <v>4.7453703703703704E-4</v>
-      </c>
-      <c r="P45" s="4">
-        <v>1.0300925925925926E-3</v>
-      </c>
-      <c r="Q45" s="5">
-        <v>2.2599999999999999E-2</v>
-      </c>
-      <c r="R45" s="5">
-        <v>2.1700000000000001E-2</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
-      <c r="V45" s="5">
-        <v>1</v>
-      </c>
-      <c r="W45">
-        <v>42.174500000000002</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B46">
-        <v>13</v>
-      </c>
-      <c r="C46">
-        <v>71</v>
-      </c>
-      <c r="D46">
-        <v>110</v>
-      </c>
-      <c r="E46" t="s">
-        <v>23</v>
-      </c>
-      <c r="F46">
-        <v>14693</v>
-      </c>
-      <c r="G46">
-        <v>10</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>1704</v>
-      </c>
-      <c r="J46">
-        <v>17</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46" s="4">
-        <v>1.1458333333333333E-3</v>
-      </c>
-      <c r="P46" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" t="s">
-        <v>25</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46" t="s">
-        <v>25</v>
-      </c>
-      <c r="V46" t="s">
-        <v>25</v>
-      </c>
-      <c r="W46">
-        <v>2.1067999999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B47">
-        <v>15</v>
-      </c>
-      <c r="C47">
-        <v>70</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47" t="s">
-        <v>26</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
-      </c>
-      <c r="J47">
-        <v>1</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="P47" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>1</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" t="s">
-        <v>25</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47" t="s">
-        <v>25</v>
-      </c>
-      <c r="W47">
-        <v>4.3400000000000001E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B48">
-        <v>15</v>
-      </c>
-      <c r="C48">
-        <v>71</v>
-      </c>
-      <c r="D48">
-        <v>110</v>
-      </c>
-      <c r="E48" t="s">
-        <v>23</v>
-      </c>
-      <c r="F48">
-        <v>14693</v>
-      </c>
-      <c r="G48">
-        <v>10</v>
-      </c>
-      <c r="H48">
-        <v>2</v>
-      </c>
-      <c r="I48">
-        <v>7644</v>
-      </c>
-      <c r="J48">
-        <v>185</v>
-      </c>
-      <c r="K48">
-        <v>12</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>10</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48" s="4">
-        <v>4.7453703703703704E-4</v>
-      </c>
-      <c r="P48" s="4">
-        <v>1.5393518518518519E-3</v>
-      </c>
-      <c r="Q48" s="5">
-        <v>2.4199999999999999E-2</v>
-      </c>
-      <c r="R48" s="5">
-        <v>6.4899999999999999E-2</v>
-      </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>2</v>
-      </c>
-      <c r="U48" s="5">
-        <v>0.16669999999999999</v>
-      </c>
-      <c r="V48" s="5">
-        <v>0.83330000000000004</v>
-      </c>
-      <c r="W48">
-        <v>28.229600000000001</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
